--- a/data/samples/products.xlsx
+++ b/data/samples/products.xlsx
@@ -429,42 +429,42 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>variety</t>
+          <t>grade</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>grade</t>
+          <t>stem_length</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>stem_length</t>
+          <t>unit</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>base_cost</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>base_cost</t>
+          <t>current_stock</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>current_stock</t>
+          <t>sale_enabled</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>sale_enabled</t>
+          <t>last_price</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>last_price</t>
+          <t>recommended_price</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -491,40 +491,38 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>红色月季A级</t>
+          <t>艾莎</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rose</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>60cm</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>bundle</t>
-        </is>
+          <t>扎</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>10</v>
-      </c>
-      <c r="H2" t="n">
         <v>50</v>
       </c>
-      <c r="I2" t="b">
+      <c r="H2" t="b">
         <v>1</v>
       </c>
+      <c r="I2" t="n">
+        <v>14</v>
+      </c>
       <c r="J2" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -550,40 +548,38 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>白色月季B级</t>
+          <t>艾莎</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>rose</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>50cm</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>bundle</t>
-        </is>
+          <t>扎</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>10</v>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
-      </c>
-      <c r="H3" t="n">
         <v>0</v>
       </c>
-      <c r="I3" t="b">
+      <c r="H3" t="b">
         <v>1</v>
       </c>
+      <c r="I3" t="n">
+        <v>13</v>
+      </c>
       <c r="J3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -609,40 +605,38 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>粉色月季A级</t>
+          <t>卡布奇诺</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>rose</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>70cm</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>bundle</t>
-        </is>
+          <t>扎</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>10</v>
       </c>
       <c r="G4" t="n">
         <v>12</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
         <v>12</v>
       </c>
-      <c r="I4" t="b">
-        <v>0</v>
-      </c>
       <c r="J4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>

--- a/data/samples/products.xlsx
+++ b/data/samples/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,14 +566,20 @@
           <t>扎</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="b">
-        <v>1</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="I3" t="n">
         <v>13</v>
@@ -651,6 +657,100 @@
       <c r="M4" t="inlineStr">
         <is>
           <t>pink</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ZIXIA-B-FG-Z</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>紫霞仙子</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>跟随等级</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>扎</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>通过业务输入录入库存</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ZIXIA-0-FG-Z</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>紫霞仙子</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>跟随等级</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>扎</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>通过业务输入录入库存</t>
         </is>
       </c>
     </row>

--- a/data/samples/products.xlsx
+++ b/data/samples/products.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SKU-001</t>
+          <t>AISHA-A-70-Z</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -543,7 +543,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SKU-002</t>
+          <t>AISHA-B-60-Z</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -606,7 +606,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SKU-003</t>
+          <t>CAPPUCCINO-A-70-Z</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>跟随等级</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -725,7 +725,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>跟随等级</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -745,14 +745,300 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>通过业务输入录入库存</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AISHA-C-55-Z</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>艾莎</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>扎</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>通过业务输入录入库存</t>
         </is>
       </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AISHA-D-50-Z</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>艾莎</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>扎</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>通过业务输入录入库存</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CAPPUCCINO-B-60-Z</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>卡布奇诺</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>扎</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>通过业务输入录入库存</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>CAPPUCCINO-C-55-Z</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>卡布奇诺</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>扎</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>通过业务输入录入库存</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CAPPUCCINO-D-50-Z</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>卡布奇诺</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>扎</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>通过业务输入录入库存</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CAPPUCCINO-E-45-Z</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>卡布奇诺</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>扎</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>通过业务输入录入库存</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/samples/products.xlsx
+++ b/data/samples/products.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1030,15 +1030,62 @@
           <t>True</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>通过业务输入录入库存</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AISHA-E-45-Z</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>艾莎</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>扎</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>通过业务输入录入库存</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
